--- a/output/pdf_financials_xlsx/SRQ.xlsx
+++ b/output/pdf_financials_xlsx/SRQ.xlsx
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.555948</v>
+        <v>-0.555948</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.549515</v>
+        <v>-1.549515</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.789183</v>
+        <v>-1.789183</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.727677</v>
+        <v>-1.727677</v>
       </c>
     </row>
     <row r="17">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.555948</v>
+        <v>-0.555948</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.549515</v>
+        <v>-1.549515</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.789183</v>
+        <v>-1.789183</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.727677</v>
+        <v>-1.727677</v>
       </c>
     </row>
     <row r="21">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.555948</v>
+        <v>-0.555948</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.549515</v>
+        <v>-1.549515</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.789183</v>
+        <v>-1.789183</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.727677</v>
+        <v>-1.727677</v>
       </c>
     </row>
     <row r="24">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>18.5316</v>
+        <v>-18.5316</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>22.135929</v>
+        <v>-22.135929</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>29.819717</v>
+        <v>-29.819717</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>43.191925</v>
+        <v>-43.191925</v>
       </c>
     </row>
     <row r="27">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.555948</v>
+        <v>-0.555948</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.549515</v>
+        <v>-1.549515</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.789183</v>
+        <v>-1.789183</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.727677</v>
+        <v>-1.727677</v>
       </c>
     </row>
     <row r="28">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.556443</v>
+        <v>-0.555453</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.563827</v>
+        <v>-1.535203</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.834687</v>
+        <v>-1.743679</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.769862</v>
+        <v>-1.685492</v>
       </c>
     </row>
     <row r="30">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6604,10 +6604,10 @@
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1.789183</v>
+        <v>-1.789183</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>1.727677</v>
+        <v>-1.727677</v>
       </c>
     </row>
     <row r="100">
@@ -7368,13 +7368,13 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0.555948</v>
+        <v>-0.555948</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>1.549515</v>
+        <v>-1.549515</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>1.789183</v>
+        <v>-1.789183</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SRQ.xlsx
+++ b/output/pdf_financials_xlsx/SRQ.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000232</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.033212</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018372</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.026942</v>
       </c>
     </row>
     <row r="13">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.555948</v>
+        <v>-0.555716</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.549515</v>
+        <v>-1.516303</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.789183</v>
+        <v>-1.770811</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.727677</v>
+        <v>-1.700735</v>
       </c>
     </row>
     <row r="28">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.555453</v>
+        <v>-0.555221</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.535203</v>
+        <v>-1.501991</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.743679</v>
+        <v>-1.725307</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.685492</v>
+        <v>-1.65855</v>
       </c>
     </row>
     <row r="30">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">

--- a/output/pdf_financials_xlsx/SRQ.xlsx
+++ b/output/pdf_financials_xlsx/SRQ.xlsx
@@ -5666,7 +5666,11 @@
           <t>Issuance of shares as part of a private placement 9</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -5890,7 +5894,11 @@
           <t>Issuance of shares as part of a private placement 10</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
